--- a/tally_templates/TMPZ.xlsx
+++ b/tally_templates/TMPZ.xlsx
@@ -1369,7 +1369,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac x16r2">
   <numFmts count="6">
     <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * -#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="mm&quot;월&quot; dd&quot;일&quot;"/>
@@ -3737,7 +3737,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="635">
+  <cellXfs count="645">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -5661,6 +5661,38 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="109" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5668,11 +5700,11 @@
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <ns3:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <ns4:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -6052,7 +6084,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I84"/>
   <sheetFormatPr defaultRowHeight="17.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
   <cols>
@@ -6173,7 +6205,7 @@
       <c r="G8" s="380" t="s">
         <v>9</v>
       </c>
-      <c r="H8" s="28" t="s">
+      <c r="H8" s="638" t="s">
         <v>162</v>
       </c>
       <c r="I8" s="28"/>
@@ -6687,7 +6719,7 @@
       <c r="G50" s="380" t="s">
         <v>9</v>
       </c>
-      <c r="H50" s="28" t="s">
+      <c r="H50" s="638" t="s">
         <v>162</v>
       </c>
       <c r="I50" s="28"/>
@@ -7194,7 +7226,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="59"/>
     <pageSetUpPr fitToPage="1"/>
@@ -7229,7 +7261,7 @@
       <c r="O1" s="4"/>
       <c r="P1" s="4"/>
     </row>
-    <row r="2" ht="22.15" customHeight="1" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="2" ht="24.3" customHeight="1" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C2" s="5" t="s">
         <v>1</v>
       </c>
@@ -7248,7 +7280,7 @@
       <c r="A4" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="635" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="9"/>
@@ -7263,7 +7295,7 @@
       <c r="J4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="1"/>
+      <c r="K4" s="636"/>
       <c r="L4" s="11">
         <v>46228</v>
       </c>
@@ -7279,7 +7311,7 @@
       <c r="A6" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="636" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="1"/>
@@ -7288,13 +7320,13 @@
       <c r="F6" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="16"/>
+      <c r="G6" s="637"/>
       <c r="H6" s="16"/>
       <c r="I6" s="16"/>
       <c r="J6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K6" s="1"/>
+      <c r="K6" s="636"/>
       <c r="L6" s="17" t="s">
         <v>10</v>
       </c>
@@ -8568,7 +8600,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="59"/>
     <pageSetUpPr fitToPage="1"/>
@@ -8688,7 +8720,7 @@
       <c r="A8" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="241" t="s">
         <v>37</v>
       </c>
       <c r="C8" s="8"/>
@@ -8697,7 +8729,7 @@
       <c r="I8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="J8" s="238"/>
+      <c r="J8" s="241"/>
       <c r="K8" s="8" t="s">
         <v>42</v>
       </c>
@@ -8713,7 +8745,7 @@
       <c r="R8" s="238"/>
     </row>
     <row r="9" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10" ht="12" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="246" t="s">
         <v>12</v>
       </c>
@@ -8747,7 +8779,7 @@
       <c r="Q10" s="235"/>
       <c r="R10" s="298"/>
     </row>
-    <row r="11" ht="12" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="251"/>
       <c r="B11" s="251"/>
       <c r="C11" s="299"/>
@@ -8770,32 +8802,18 @@
       <c r="R11" s="301"/>
     </row>
     <row r="12" ht="21" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" s="302" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="302" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="303" t="s">
-        <v>86</v>
-      </c>
+      <c r="A12" s="302"/>
+      <c r="B12" s="302"/>
+      <c r="C12" s="303"/>
       <c r="D12" s="304"/>
       <c r="E12" s="305"/>
-      <c r="F12" s="303" t="s">
-        <v>87</v>
-      </c>
+      <c r="F12" s="303"/>
       <c r="G12" s="304"/>
       <c r="H12" s="304"/>
       <c r="I12" s="305"/>
-      <c r="J12" s="302">
-        <v>1</v>
-      </c>
-      <c r="K12" s="302" t="s">
-        <v>71</v>
-      </c>
-      <c r="L12" s="306" t="s">
-        <v>88</v>
-      </c>
+      <c r="J12" s="302"/>
+      <c r="K12" s="302"/>
+      <c r="L12" s="306"/>
       <c r="M12" s="307"/>
       <c r="N12" s="307"/>
       <c r="O12" s="307"/>
@@ -8804,32 +8822,18 @@
       <c r="R12" s="308"/>
     </row>
     <row r="13" ht="21" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A13" s="309" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="309" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="310" t="s">
-        <v>89</v>
-      </c>
+      <c r="A13" s="309"/>
+      <c r="B13" s="309"/>
+      <c r="C13" s="310"/>
       <c r="D13" s="311"/>
       <c r="E13" s="312"/>
-      <c r="F13" s="284" t="s">
-        <v>87</v>
-      </c>
+      <c r="F13" s="284"/>
       <c r="G13" s="313"/>
       <c r="H13" s="313"/>
       <c r="I13" s="285"/>
-      <c r="J13" s="309">
-        <v>1</v>
-      </c>
-      <c r="K13" s="309" t="s">
-        <v>71</v>
-      </c>
-      <c r="L13" s="314" t="s">
-        <v>90</v>
-      </c>
+      <c r="J13" s="309"/>
+      <c r="K13" s="309"/>
+      <c r="L13" s="314"/>
       <c r="M13" s="315"/>
       <c r="N13" s="315"/>
       <c r="O13" s="315"/>
@@ -9204,7 +9208,7 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H74"/>
   <sheetFormatPr defaultRowHeight="17.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
   <cols>
@@ -9285,7 +9289,7 @@
       <c r="E6" s="378" t="s">
         <v>140</v>
       </c>
-      <c r="F6" s="381" t="s">
+      <c r="F6" s="644" t="s">
         <v>37</v>
       </c>
     </row>
@@ -9669,7 +9673,7 @@
       <c r="E43" s="378" t="s">
         <v>140</v>
       </c>
-      <c r="F43" s="381" t="s">
+      <c r="F43" s="644" t="s">
         <v>37</v>
       </c>
     </row>
@@ -9992,7 +9996,7 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -10082,7 +10086,7 @@
       <c r="A8" s="193" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="197" t="s">
+      <c r="B8" s="638" t="s">
         <v>42</v>
       </c>
       <c r="C8" s="198"/>
@@ -10097,7 +10101,7 @@
       <c r="G8" s="199" t="s">
         <v>44</v>
       </c>
-      <c r="H8" s="200" t="s">
+      <c r="H8" s="639" t="s">
         <v>45</v>
       </c>
     </row>
@@ -10466,7 +10470,7 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="59"/>
     <pageSetUpPr fitToPage="1"/>
@@ -10549,14 +10553,14 @@
       <c r="G6" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H6" s="238" t="s">
+      <c r="H6" s="241" t="s">
         <v>55</v>
       </c>
       <c r="I6" s="238"/>
       <c r="K6" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="L6" s="240">
+      <c r="L6" s="640">
         <v>46227</v>
       </c>
       <c r="M6" s="238"/>
@@ -10569,7 +10573,7 @@
       <c r="A8" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="641" t="s">
         <v>37</v>
       </c>
       <c r="C8" s="242"/>
@@ -10577,7 +10581,7 @@
       <c r="G8" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="H8" s="238" t="s">
+      <c r="H8" s="241" t="s">
         <v>42</v>
       </c>
       <c r="I8" s="238"/>
@@ -11149,7 +11153,7 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="59"/>
     <pageSetUpPr fitToPage="1"/>
@@ -11232,7 +11236,7 @@
       <c r="G6" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H6" s="238" t="s">
+      <c r="H6" s="241" t="s">
         <v>92</v>
       </c>
       <c r="I6" s="238"/>
@@ -11254,7 +11258,7 @@
       <c r="A8" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="641" t="s">
         <v>37</v>
       </c>
       <c r="C8" s="242"/>
@@ -11262,7 +11266,7 @@
       <c r="G8" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="H8" s="238" t="s">
+      <c r="H8" s="241" t="s">
         <v>42</v>
       </c>
       <c r="I8" s="238"/>
@@ -11878,7 +11882,7 @@
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M88"/>
   <sheetFormatPr defaultRowHeight="13.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
   <cols>
@@ -11996,22 +12000,18 @@
       <c r="A8" s="37" t="s">
         <v>100</v>
       </c>
-      <c r="B8" s="37"/>
-      <c r="C8" s="193" t="s">
-        <v>86</v>
-      </c>
+      <c r="B8" s="642"/>
+      <c r="C8" s="193"/>
       <c r="E8" s="28" t="s">
         <v>101</v>
       </c>
       <c r="F8" s="28"/>
-      <c r="G8" s="28" t="s">
-        <v>102</v>
-      </c>
+      <c r="G8" s="638"/>
       <c r="H8" s="28"/>
       <c r="J8" s="193" t="s">
         <v>103</v>
       </c>
-      <c r="K8" s="28" t="s">
+      <c r="K8" s="638" t="s">
         <v>15</v>
       </c>
       <c r="L8" s="28" t="s">
@@ -12025,7 +12025,7 @@
       <c r="A9" s="37" t="s">
         <v>104</v>
       </c>
-      <c r="B9" s="37"/>
+      <c r="B9" s="642"/>
       <c r="C9" s="193" t="s">
         <v>105</v>
       </c>
@@ -12139,7 +12139,7 @@
       </c>
       <c r="B28" s="351"/>
       <c r="C28" s="351"/>
-      <c r="D28" s="352"/>
+      <c r="D28" s="643"/>
       <c r="E28" s="352"/>
       <c r="F28" s="352"/>
       <c r="G28" s="352"/>
@@ -12168,9 +12168,7 @@
     </row>
     <row r="30" ht="22.15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="355"/>
-      <c r="B30" s="356" t="s">
-        <v>88</v>
-      </c>
+      <c r="B30" s="356"/>
       <c r="C30" s="356"/>
       <c r="D30" s="356"/>
       <c r="E30" s="356"/>
@@ -12523,22 +12521,18 @@
       <c r="A52" s="37" t="s">
         <v>100</v>
       </c>
-      <c r="B52" s="37"/>
-      <c r="C52" s="193" t="s">
-        <v>89</v>
-      </c>
+      <c r="B52" s="642"/>
+      <c r="C52" s="193"/>
       <c r="E52" s="28" t="s">
         <v>101</v>
       </c>
       <c r="F52" s="28"/>
-      <c r="G52" s="28" t="s">
-        <v>102</v>
-      </c>
+      <c r="G52" s="638"/>
       <c r="H52" s="28"/>
       <c r="J52" s="193" t="s">
         <v>103</v>
       </c>
-      <c r="K52" s="28" t="s">
+      <c r="K52" s="638" t="s">
         <v>15</v>
       </c>
       <c r="L52" s="28" t="s">
@@ -12552,7 +12546,7 @@
       <c r="A53" s="37" t="s">
         <v>104</v>
       </c>
-      <c r="B53" s="37"/>
+      <c r="B53" s="642"/>
       <c r="C53" s="193" t="s">
         <v>105</v>
       </c>
@@ -12666,7 +12660,7 @@
       </c>
       <c r="B72" s="351"/>
       <c r="C72" s="351"/>
-      <c r="D72" s="352"/>
+      <c r="D72" s="643"/>
       <c r="E72" s="352"/>
       <c r="F72" s="352"/>
       <c r="G72" s="352"/>
@@ -12695,9 +12689,7 @@
     </row>
     <row r="74" ht="22.15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="355"/>
-      <c r="B74" s="356" t="s">
-        <v>90</v>
-      </c>
+      <c r="B74" s="356"/>
       <c r="C74" s="356"/>
       <c r="D74" s="356"/>
       <c r="E74" s="356"/>
@@ -13021,7 +13013,7 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AK86"/>
   <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
   <cols>
@@ -13241,7 +13233,7 @@
       <c r="A6" s="37" t="s">
         <v>180</v>
       </c>
-      <c r="B6" s="37"/>
+      <c r="B6" s="642"/>
       <c r="C6" s="37"/>
       <c r="D6" s="339" t="str">
         <f>'Final Work'!B4</f>
@@ -13330,7 +13322,7 @@
       <c r="A8" s="186" t="s">
         <v>181</v>
       </c>
-      <c r="B8" s="186"/>
+      <c r="B8" s="643"/>
       <c r="C8" s="186"/>
       <c r="D8" s="351" t="s">
         <v>42</v>
@@ -13348,7 +13340,7 @@
       <c r="O8" s="351" t="s">
         <v>8</v>
       </c>
-      <c r="P8" s="186"/>
+      <c r="P8" s="643"/>
       <c r="Q8" s="186"/>
       <c r="R8" s="352">
         <f>'Final Work'!G6</f>
@@ -13365,7 +13357,7 @@
       </c>
       <c r="Z8" s="352"/>
       <c r="AA8" s="352"/>
-      <c r="AB8" s="352" t="s">
+      <c r="AB8" s="643" t="s">
         <v>37</v>
       </c>
       <c r="AC8" s="352"/>
@@ -17155,7 +17147,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="59"/>
     <pageSetUpPr fitToPage="1"/>
@@ -17273,7 +17265,7 @@
       <c r="A8" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="241" t="s">
         <v>37</v>
       </c>
       <c r="C8" s="8"/>
@@ -17282,7 +17274,7 @@
       <c r="I8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="J8" s="238"/>
+      <c r="J8" s="241"/>
       <c r="K8" s="8" t="s">
         <v>42</v>
       </c>
@@ -17298,7 +17290,7 @@
       <c r="R8" s="238"/>
     </row>
     <row r="9" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10" ht="12" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="246" t="s">
         <v>12</v>
       </c>
@@ -17332,7 +17324,7 @@
       <c r="Q10" s="235"/>
       <c r="R10" s="298"/>
     </row>
-    <row r="11" ht="12" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="251"/>
       <c r="B11" s="251"/>
       <c r="C11" s="299"/>
